--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-nabm.xlsx
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V98</t>
+    <t>V99</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T00:00:00+00:00</t>
+    <t>2025-09-08T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4343,7 +4343,7 @@
     <t>4103</t>
   </si>
   <si>
-    <t>TEST DE DETECTION DE LA PRODUCTION D'INTERFERON GAMMA (IGRA)</t>
+    <t>IGRA:TEST DE DETECTION DE LA PRODUCTION D'INTERFERON GAMMA</t>
   </si>
   <si>
     <t>0290</t>
